--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0031.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0031.xlsx
@@ -19952,7 +19952,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>R?i ?i!</t>
+          <t>Rời đi!</t>
         </is>
       </c>
     </row>
@@ -22227,7 +22227,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Cảm ơn, để ta đi quanh xem sao.</t>
+          <t>Cảm ơn, để tao đi quanh xem sao.</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>"Nhắc mới nhớ, ta có một mẹo cho ngươi... &lt;color=red&gt;Starting from Theater 2, all the film endings can be changed.&lt;/color&gt;"</t>
+          <t>"Nhắc mới nhớ, ta có một mẹo cho ngươi... &lt;color=red&gt;Từ Nhà hát 2 trở đi, mọi kết thúc phim đều có thể thay đổi được.&lt;/color&gt;"</t>
         </is>
       </c>
     </row>
